--- a/public/Excel_Var1_Starter.xlsx
+++ b/public/Excel_Var1_Starter.xlsx
@@ -347,6 +347,16 @@
           <t>CSN SOC 101 - Grade Book</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Total Points Possible</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="P2" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="1">
       <c r="A3" s="2" t="inlineStr">
@@ -414,11 +424,7 @@
           <t>Feedback</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Total Points Possible</t>
-        </is>
-      </c>
+      <c r="P3" s="2" t="n"/>
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>Report Generated:</t>
@@ -451,9 +457,7 @@
       <c r="G4" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="P4" s="2" t="n">
-        <v>300</v>
-      </c>
+      <c r="P4" s="2" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="1">
       <c r="A5" s="2" t="inlineStr">

--- a/public/Excel_Var1_Starter.xlsx
+++ b/public/Excel_Var1_Starter.xlsx
@@ -347,14 +347,19 @@
           <t>CSN SOC 101 - Grade Book</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Total Points Possible</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Report Generated:</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>300</v>
       </c>
     </row>

--- a/public/Excel_Var1_Starter.xlsx
+++ b/public/Excel_Var1_Starter.xlsx
@@ -352,7 +352,7 @@
           <t>Total Points Possible</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Report Generated:</t>
         </is>
@@ -570,6 +570,11 @@
       </c>
       <c r="G8" s="2" t="n">
         <v>85</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Look Up Student:</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="1">
